--- a/docs/downloads/05/tbl_water_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_water_marovoay_tous.xlsx
@@ -405,12 +405,6 @@
           <t>Puits (margelle)</t>
         </is>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>2.8</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -495,12 +489,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -513,12 +501,6 @@
           <t>Impluvium</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -603,12 +585,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -621,12 +597,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,12 +609,6 @@
           <t>Puits (margelle)</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -711,12 +675,6 @@
           <t>Puits (margelle)</t>
         </is>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -729,12 +687,6 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -783,12 +735,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -800,12 +746,6 @@
         <is>
           <t>Impluvium</t>
         </is>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>0.2</v>
       </c>
     </row>
     <row r="26">

--- a/docs/downloads/05/tbl_water_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_water_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
